--- a/output_boron/boron_Intermediate_seki_2010.xlsx
+++ b/output_boron/boron_Intermediate_seki_2010.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1016/j.epsl.2010.01.037</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_seki_2010.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_seki_2010_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1507,7 +1507,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1567,12 +1567,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1686,7 +1680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1768,7 +1762,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2375,7 +2368,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2452,7 +2445,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2529,7 +2522,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2606,7 +2599,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2683,7 +2676,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2760,7 +2753,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2837,7 +2830,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2914,7 +2907,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2991,7 +2984,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3068,7 +3061,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3145,7 +3138,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3222,7 +3215,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3299,7 +3292,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3376,7 +3369,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3453,7 +3446,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3530,7 +3523,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3607,7 +3600,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3684,7 +3677,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3761,7 +3754,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3838,7 +3831,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -4160,28 +4153,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
